--- a/processed/MRNGO_mini-norm_richness_excel.xlsx
+++ b/processed/MRNGO_mini-norm_richness_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/illesanna/Desktop/DOKUMENTUMOK/ELTE/SZAKDOLGOZAT/data/MRNGO_mini-norm/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90E0D86B-6470-714D-AC7E-3A8F8555EB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{70201BF7-F1EB-F848-B5BA-4C72726E218B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16840" xr2:uid="{22538D9A-B7C4-794D-8543-265CC3D0B396}"/>
+    <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16480" xr2:uid="{22538D9A-B7C4-794D-8543-265CC3D0B396}"/>
   </bookViews>
   <sheets>
     <sheet name="MRNGO_mini-norm_richness" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="190" uniqueCount="190">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="191" uniqueCount="191">
   <si>
     <t>Concept</t>
   </si>
@@ -595,13 +595,16 @@
   </si>
   <si>
     <t>0.617456236993512</t>
+  </si>
+  <si>
+    <t>natural</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -754,6 +757,22 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -936,7 +955,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <start/>
       <end/>
@@ -1051,6 +1070,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <start/>
+      <end/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1096,8 +1124,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - 1. jelölőszín" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1473,1091 +1503,1184 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{441BDA1D-5500-464C-9E6E-192CB131A680}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>58</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>13</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>15</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>90</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>203</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>15</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>113</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>22</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>14</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>148</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>232</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>89</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>9</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>14</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>123</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>222</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>24</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>25</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>26</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>27</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>29</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5">
         <v>92</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>14</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>16</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>115</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>168</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>30</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>31</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>32</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>33</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>85</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>22</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>15</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>124</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>220</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>36</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>37</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>38</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>39</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>41</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>94</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>21</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>16</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>138</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>246</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>42</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>43</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>44</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>45</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>47</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8">
         <v>104</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>14</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>16</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>130</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>203</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>48</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>49</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>50</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>51</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>53</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9">
         <v>102</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>20</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>15</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>140</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>244</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>54</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>55</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>56</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>57</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>59</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10">
         <v>152</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>19</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>16</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>190</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>287</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>760</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>60</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>61</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>62</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>64</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11">
         <v>76</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>13</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>15</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>104</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>193</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>65</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>66</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>67</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>68</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>70</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12">
         <v>127</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>24</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>15</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>177</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>290</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>71</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>72</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>73</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>74</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>76</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>117</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>19</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>16</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>157</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>251</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>77</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>78</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>79</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>80</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>82</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14">
         <v>93</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>11</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>15</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>116</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>177</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>83</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>84</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>85</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>86</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>88</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>88</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>13</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>15</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>114</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>192</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>89</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>90</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>91</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>92</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>94</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+      <c r="C16">
         <v>89</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>13</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>15</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>126</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>228</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>95</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>96</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>97</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>98</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>100</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>67</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>10</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>14</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>93</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>167</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>101</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>102</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>103</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>104</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>106</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+      <c r="C18">
         <v>89</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>12</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>14</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>113</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>179</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>107</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>108</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>109</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>110</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>112</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>114</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>19</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>16</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>151</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>243</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>113</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>114</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>115</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>116</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>118</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20">
         <v>101</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>17</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>16</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>132</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>210</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>119</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>120</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>121</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>122</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>124</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+      <c r="C21">
         <v>132</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>20</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>16</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>179</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>322</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>125</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>126</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>127</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>128</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>130</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+      <c r="C22">
         <v>79</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>19</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>16</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>117</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>212</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>131</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>132</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>133</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>134</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>136</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23">
         <v>130</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>22</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>16</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>177</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>328</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>137</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>138</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>139</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>140</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>142</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24">
         <v>87</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>17</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>16</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>118</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>187</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>143</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>144</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>145</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>146</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>148</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25">
         <v>66</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>9</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>16</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>93</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>186</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>149</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>150</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>151</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>152</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>154</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26">
         <v>94</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>22</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>15</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>136</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>225</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>155</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>156</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>157</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>158</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>160</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27">
         <v>95</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>14</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>16</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>120</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>191</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>161</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>162</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>163</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>164</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>166</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
+        <v>1</v>
+      </c>
+      <c r="C28">
         <v>94</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>17</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>16</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>124</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>206</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>167</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>168</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>169</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>170</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>172</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29">
         <v>93</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>12</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>15</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>117</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>167</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>173</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>174</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>175</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>176</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>178</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
+        <v>1</v>
+      </c>
+      <c r="C30">
         <v>123</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>18</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>17</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>162</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>270</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>179</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>180</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>181</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>182</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>184</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31">
         <v>100</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>28</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>16</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>145</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>252</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>185</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>186</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>187</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>188</v>
       </c>
-      <c r="K31" t="s">
+      <c r="L31" t="s">
         <v>189</v>
       </c>
     </row>
